--- a/test/fixtures/timetrackers/adversarial.xlsx
+++ b/test/fixtures/timetrackers/adversarial.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="TimeTracker" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Time" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="82">
   <si>
     <t>Employee Name</t>
   </si>
@@ -22,15 +22,9 @@
     <t>Time Tracker Start Date</t>
   </si>
   <si>
-    <t>2026-04-27</t>
-  </si>
-  <si>
     <t>Time Tracker End Date</t>
   </si>
   <si>
-    <t>2026-05-03</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
@@ -52,80 +46,236 @@
     <t>Duration</t>
   </si>
   <si>
+    <t>Time Range</t>
+  </si>
+  <si>
     <t>Notes</t>
   </si>
   <si>
-    <t>2026-04-29</t>
+    <t>James F. Kimmel &amp; Associates</t>
+  </si>
+  <si>
+    <t>Tax Return Preparation</t>
   </si>
   <si>
     <t>Acme Corp</t>
   </si>
   <si>
-    <t>Tax Compliance</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
-    <t>sent invoice copy to John Smith at john.smith@example.com</t>
+    <t>8:00-9:00</t>
+  </si>
+  <si>
+    <t>sent invoice copy to John Smith at john.smith@example.com [1]</t>
+  </si>
+  <si>
+    <t>Monthly Services</t>
   </si>
   <si>
     <t>Globex Industries</t>
   </si>
   <si>
-    <t>Bookkeeping</t>
-  </si>
-  <si>
-    <t>called (555) 123-4567 and confirmed the appointment</t>
-  </si>
-  <si>
-    <t>Smith, John</t>
-  </si>
-  <si>
-    <t>Consulting</t>
-  </si>
-  <si>
-    <t>reviewed SSN 123-45-6789 on the W-9 form</t>
-  </si>
-  <si>
-    <t>Smith, Jane</t>
-  </si>
-  <si>
-    <t>discussed payment with Acme Corp CFO</t>
-  </si>
-  <si>
-    <t>Wayne Enterprises</t>
-  </si>
-  <si>
-    <t>mailed package to 123 Main St, Phoenix, AZ 85003</t>
-  </si>
-  <si>
-    <t>wired $1,200 to bank account 0123456789</t>
-  </si>
-  <si>
-    <t>text from +1 (480) 555-0199 about deadline</t>
-  </si>
-  <si>
-    <t>forwarded email from cfo@globex.com</t>
-  </si>
-  <si>
-    <t>follow-up note: Eliza Smith handled the audit prep</t>
-  </si>
-  <si>
-    <t>paid by card 4111-1111-1111-1111 ending 1111</t>
+    <t>9:00-10:00</t>
+  </si>
+  <si>
+    <t>called (555) 123-4567 and confirmed the appointment [2]</t>
+  </si>
+  <si>
+    <t>Phone Call</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Smith</t>
+  </si>
+  <si>
+    <t>10:00-11:00</t>
+  </si>
+  <si>
+    <t>reviewed SSN 123-45-6789 on the W-9 form [3]</t>
+  </si>
+  <si>
+    <t>11:00-12:00</t>
+  </si>
+  <si>
+    <t>discussed payment with Acme Corp CFO [4]</t>
+  </si>
+  <si>
+    <t>12:00-13:00</t>
+  </si>
+  <si>
+    <t>mailed package to 123 Main St, Phoenix, AZ 85003 [5]</t>
+  </si>
+  <si>
+    <t>13:00-14:00</t>
+  </si>
+  <si>
+    <t>wired $1,200 to bank account 0123456789 [6]</t>
+  </si>
+  <si>
+    <t>14:00-15:00</t>
+  </si>
+  <si>
+    <t>text from +1 (480) 555-0199 about deadline [7]</t>
+  </si>
+  <si>
+    <t>15:00-16:00</t>
+  </si>
+  <si>
+    <t>forwarded email from cfo@globex.com [8]</t>
+  </si>
+  <si>
+    <t>16:00-17:00</t>
+  </si>
+  <si>
+    <t>follow-up note: Eliza Smith handled the audit prep [9]</t>
+  </si>
+  <si>
+    <t>17:00-18:00</t>
+  </si>
+  <si>
+    <t>paid by card 4111-1111-1111-1111 ending 1111 [10]</t>
+  </si>
+  <si>
+    <t>18:00-19:00</t>
+  </si>
+  <si>
+    <t>sent invoice copy to John Smith at john.smith@example.com [11]</t>
+  </si>
+  <si>
+    <t>19:00-20:00</t>
+  </si>
+  <si>
+    <t>called (555) 123-4567 and confirmed the appointment [12]</t>
+  </si>
+  <si>
+    <t>20:00-21:00</t>
+  </si>
+  <si>
+    <t>reviewed SSN 123-45-6789 on the W-9 form [13]</t>
+  </si>
+  <si>
+    <t>21:00-22:00</t>
+  </si>
+  <si>
+    <t>discussed payment with Acme Corp CFO [14]</t>
+  </si>
+  <si>
+    <t>22:00-23:00</t>
+  </si>
+  <si>
+    <t>mailed package to 123 Main St, Phoenix, AZ 85003 [15]</t>
+  </si>
+  <si>
+    <t>23:00-24:00</t>
+  </si>
+  <si>
+    <t>wired $1,200 to bank account 0123456789 [16]</t>
+  </si>
+  <si>
+    <t>24:00-25:00</t>
+  </si>
+  <si>
+    <t>text from +1 (480) 555-0199 about deadline [17]</t>
+  </si>
+  <si>
+    <t>25:00-26:00</t>
+  </si>
+  <si>
+    <t>forwarded email from cfo@globex.com [18]</t>
+  </si>
+  <si>
+    <t>26:00-27:00</t>
+  </si>
+  <si>
+    <t>follow-up note: Eliza Smith handled the audit prep [19]</t>
+  </si>
+  <si>
+    <t>27:00-28:00</t>
+  </si>
+  <si>
+    <t>paid by card 4111-1111-1111-1111 ending 1111 [20]</t>
+  </si>
+  <si>
+    <t>28:00-29:00</t>
+  </si>
+  <si>
+    <t>sent invoice copy to John Smith at john.smith@example.com [21]</t>
+  </si>
+  <si>
+    <t>29:00-30:00</t>
+  </si>
+  <si>
+    <t>called (555) 123-4567 and confirmed the appointment [22]</t>
+  </si>
+  <si>
+    <t>30:00-31:00</t>
+  </si>
+  <si>
+    <t>reviewed SSN 123-45-6789 on the W-9 form [23]</t>
+  </si>
+  <si>
+    <t>31:00-32:00</t>
+  </si>
+  <si>
+    <t>discussed payment with Acme Corp CFO [24]</t>
+  </si>
+  <si>
+    <t>32:00-33:00</t>
+  </si>
+  <si>
+    <t>mailed package to 123 Main St, Phoenix, AZ 85003 [25]</t>
+  </si>
+  <si>
+    <t>33:00-34:00</t>
+  </si>
+  <si>
+    <t>wired $1,200 to bank account 0123456789 [26]</t>
+  </si>
+  <si>
+    <t>34:00-35:00</t>
+  </si>
+  <si>
+    <t>text from +1 (480) 555-0199 about deadline [27]</t>
+  </si>
+  <si>
+    <t>35:00-36:00</t>
+  </si>
+  <si>
+    <t>forwarded email from cfo@globex.com [28]</t>
+  </si>
+  <si>
+    <t>36:00-37:00</t>
+  </si>
+  <si>
+    <t>follow-up note: Eliza Smith handled the audit prep [29]</t>
+  </si>
+  <si>
+    <t>37:00-38:00</t>
+  </si>
+  <si>
+    <t>paid by card 4111-1111-1111-1111 ending 1111 [30]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -148,8 +298,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -504,915 +656,915 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>3</v>
+      <c r="B2">
+        <v>46139</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <v>46145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D5" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="F5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1</v>
-      </c>
       <c r="E6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6">
+        <v>60</v>
+      </c>
+      <c r="H6" t="s">
         <v>17</v>
-      </c>
-      <c r="F6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6">
-        <v>60</v>
       </c>
       <c r="I6" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>14</v>
+      <c r="A7" s="2">
+        <v>46141</v>
       </c>
       <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>20</v>
       </c>
-      <c r="D7" t="s">
-        <v>1</v>
-      </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7">
-        <v>60</v>
+        <v>16</v>
+      </c>
+      <c r="G7">
+        <v>60</v>
+      </c>
+      <c r="H7" t="s">
+        <v>21</v>
       </c>
       <c r="I7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>14</v>
+      <c r="A8" s="2">
+        <v>46141</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
         <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8">
-        <v>60</v>
+        <v>25</v>
+      </c>
+      <c r="G8">
+        <v>60</v>
+      </c>
+      <c r="H8" t="s">
+        <v>26</v>
       </c>
       <c r="I8" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
         <v>14</v>
       </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" t="s">
-        <v>16</v>
-      </c>
       <c r="D9" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9">
-        <v>60</v>
+        <v>16</v>
+      </c>
+      <c r="G9">
+        <v>60</v>
+      </c>
+      <c r="H9" t="s">
+        <v>28</v>
       </c>
       <c r="I9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>14</v>
+      <c r="A10" s="2">
+        <v>46141</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
         <v>20</v>
       </c>
-      <c r="D10" t="s">
-        <v>1</v>
-      </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10" t="s">
-        <v>17</v>
-      </c>
-      <c r="H10">
-        <v>60</v>
+        <v>16</v>
+      </c>
+      <c r="G10">
+        <v>60</v>
+      </c>
+      <c r="H10" t="s">
+        <v>30</v>
       </c>
       <c r="I10" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>14</v>
+      <c r="A11" s="2">
+        <v>46141</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
         <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11">
-        <v>60</v>
+        <v>25</v>
+      </c>
+      <c r="G11">
+        <v>60</v>
+      </c>
+      <c r="H11" t="s">
+        <v>32</v>
       </c>
       <c r="I11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" t="s">
         <v>14</v>
       </c>
-      <c r="B12" t="s">
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12">
+        <v>60</v>
+      </c>
+      <c r="H12" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" t="s">
         <v>19</v>
       </c>
-      <c r="C12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12">
-        <v>60</v>
-      </c>
-      <c r="I12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>20</v>
       </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F13" t="s">
-        <v>17</v>
-      </c>
-      <c r="G13" t="s">
-        <v>17</v>
-      </c>
-      <c r="H13">
-        <v>60</v>
+        <v>16</v>
+      </c>
+      <c r="G13">
+        <v>60</v>
+      </c>
+      <c r="H13" t="s">
+        <v>36</v>
       </c>
       <c r="I13" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>14</v>
+      <c r="A14" s="2">
+        <v>46141</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
         <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F14" t="s">
-        <v>17</v>
-      </c>
-      <c r="G14" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14">
-        <v>60</v>
+        <v>25</v>
+      </c>
+      <c r="G14">
+        <v>60</v>
+      </c>
+      <c r="H14" t="s">
+        <v>38</v>
       </c>
       <c r="I14" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" t="s">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" t="s">
-        <v>16</v>
-      </c>
       <c r="D15" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>17</v>
-      </c>
-      <c r="G15" t="s">
-        <v>17</v>
-      </c>
-      <c r="H15">
-        <v>60</v>
+        <v>16</v>
+      </c>
+      <c r="G15">
+        <v>60</v>
+      </c>
+      <c r="H15" t="s">
+        <v>40</v>
       </c>
       <c r="I15" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>14</v>
+      <c r="A16" s="2">
+        <v>46141</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" t="s">
         <v>20</v>
       </c>
-      <c r="D16" t="s">
-        <v>1</v>
-      </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F16" t="s">
-        <v>17</v>
-      </c>
-      <c r="G16" t="s">
-        <v>17</v>
-      </c>
-      <c r="H16">
-        <v>60</v>
+        <v>16</v>
+      </c>
+      <c r="G16">
+        <v>60</v>
+      </c>
+      <c r="H16" t="s">
+        <v>42</v>
       </c>
       <c r="I16" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>14</v>
+      <c r="A17" s="2">
+        <v>46141</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
         <v>23</v>
       </c>
       <c r="D17" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G17" t="s">
-        <v>17</v>
-      </c>
-      <c r="H17">
-        <v>60</v>
+        <v>25</v>
+      </c>
+      <c r="G17">
+        <v>60</v>
+      </c>
+      <c r="H17" t="s">
+        <v>44</v>
       </c>
       <c r="I17" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="A18" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s">
         <v>14</v>
       </c>
-      <c r="B18" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" t="s">
-        <v>16</v>
-      </c>
       <c r="D18" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G18" t="s">
-        <v>17</v>
-      </c>
-      <c r="H18">
-        <v>60</v>
+        <v>16</v>
+      </c>
+      <c r="G18">
+        <v>60</v>
+      </c>
+      <c r="H18" t="s">
+        <v>46</v>
       </c>
       <c r="I18" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>14</v>
+      <c r="A19" s="2">
+        <v>46141</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" t="s">
         <v>20</v>
       </c>
-      <c r="D19" t="s">
-        <v>1</v>
-      </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F19" t="s">
-        <v>17</v>
-      </c>
-      <c r="G19" t="s">
-        <v>17</v>
-      </c>
-      <c r="H19">
-        <v>60</v>
+        <v>16</v>
+      </c>
+      <c r="G19">
+        <v>60</v>
+      </c>
+      <c r="H19" t="s">
+        <v>48</v>
       </c>
       <c r="I19" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>14</v>
+      <c r="A20" s="2">
+        <v>46141</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C20" t="s">
         <v>23</v>
       </c>
       <c r="D20" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G20" t="s">
-        <v>17</v>
-      </c>
-      <c r="H20">
-        <v>60</v>
+        <v>25</v>
+      </c>
+      <c r="G20">
+        <v>60</v>
+      </c>
+      <c r="H20" t="s">
+        <v>50</v>
       </c>
       <c r="I20" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="A21" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" t="s">
         <v>14</v>
       </c>
-      <c r="B21" t="s">
+      <c r="D21" t="s">
         <v>15</v>
       </c>
-      <c r="C21" t="s">
-        <v>16</v>
-      </c>
-      <c r="D21" t="s">
-        <v>1</v>
-      </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F21" t="s">
-        <v>17</v>
-      </c>
-      <c r="G21" t="s">
-        <v>17</v>
-      </c>
-      <c r="H21">
-        <v>60</v>
+        <v>16</v>
+      </c>
+      <c r="G21">
+        <v>60</v>
+      </c>
+      <c r="H21" t="s">
+        <v>52</v>
       </c>
       <c r="I21" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>14</v>
+      <c r="A22" s="2">
+        <v>46141</v>
       </c>
       <c r="B22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" t="s">
         <v>19</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>20</v>
       </c>
-      <c r="D22" t="s">
-        <v>1</v>
-      </c>
       <c r="E22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F22" t="s">
-        <v>17</v>
-      </c>
-      <c r="G22" t="s">
-        <v>17</v>
-      </c>
-      <c r="H22">
-        <v>60</v>
+        <v>16</v>
+      </c>
+      <c r="G22">
+        <v>60</v>
+      </c>
+      <c r="H22" t="s">
+        <v>54</v>
       </c>
       <c r="I22" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>14</v>
+      <c r="A23" s="2">
+        <v>46141</v>
       </c>
       <c r="B23" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
         <v>23</v>
       </c>
       <c r="D23" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E23" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F23" t="s">
-        <v>17</v>
-      </c>
-      <c r="G23" t="s">
-        <v>17</v>
-      </c>
-      <c r="H23">
-        <v>60</v>
+        <v>25</v>
+      </c>
+      <c r="G23">
+        <v>60</v>
+      </c>
+      <c r="H23" t="s">
+        <v>56</v>
       </c>
       <c r="I23" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="A24" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" t="s">
         <v>14</v>
       </c>
-      <c r="B24" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" t="s">
-        <v>16</v>
-      </c>
       <c r="D24" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F24" t="s">
-        <v>17</v>
-      </c>
-      <c r="G24" t="s">
-        <v>17</v>
-      </c>
-      <c r="H24">
-        <v>60</v>
+        <v>16</v>
+      </c>
+      <c r="G24">
+        <v>60</v>
+      </c>
+      <c r="H24" t="s">
+        <v>58</v>
       </c>
       <c r="I24" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>14</v>
+      <c r="A25" s="2">
+        <v>46141</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C25" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" t="s">
         <v>20</v>
       </c>
-      <c r="D25" t="s">
-        <v>1</v>
-      </c>
       <c r="E25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G25" t="s">
-        <v>17</v>
-      </c>
-      <c r="H25">
+        <v>16</v>
+      </c>
+      <c r="G25">
+        <v>60</v>
+      </c>
+      <c r="H25" t="s">
         <v>60</v>
       </c>
       <c r="I25" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>14</v>
+      <c r="A26" s="2">
+        <v>46141</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C26" t="s">
         <v>23</v>
       </c>
       <c r="D26" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E26" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F26" t="s">
-        <v>17</v>
-      </c>
-      <c r="G26" t="s">
-        <v>17</v>
-      </c>
-      <c r="H26">
-        <v>60</v>
+        <v>25</v>
+      </c>
+      <c r="G26">
+        <v>60</v>
+      </c>
+      <c r="H26" t="s">
+        <v>62</v>
       </c>
       <c r="I26" t="s">
-        <v>18</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+      <c r="A27" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" t="s">
         <v>14</v>
       </c>
-      <c r="B27" t="s">
+      <c r="D27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" t="s">
+        <v>16</v>
+      </c>
+      <c r="G27">
+        <v>60</v>
+      </c>
+      <c r="H27" t="s">
+        <v>64</v>
+      </c>
+      <c r="I27" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B28" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" t="s">
         <v>19</v>
       </c>
-      <c r="C27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D27" t="s">
-        <v>1</v>
-      </c>
-      <c r="E27" t="s">
-        <v>17</v>
-      </c>
-      <c r="F27" t="s">
-        <v>17</v>
-      </c>
-      <c r="G27" t="s">
-        <v>17</v>
-      </c>
-      <c r="H27">
-        <v>60</v>
-      </c>
-      <c r="I27" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" t="s">
-        <v>22</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>20</v>
       </c>
-      <c r="D28" t="s">
-        <v>1</v>
-      </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F28" t="s">
-        <v>17</v>
-      </c>
-      <c r="G28" t="s">
-        <v>17</v>
-      </c>
-      <c r="H28">
-        <v>60</v>
+        <v>16</v>
+      </c>
+      <c r="G28">
+        <v>60</v>
+      </c>
+      <c r="H28" t="s">
+        <v>66</v>
       </c>
       <c r="I28" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>14</v>
+      <c r="A29" s="2">
+        <v>46141</v>
       </c>
       <c r="B29" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C29" t="s">
         <v>23</v>
       </c>
       <c r="D29" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E29" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F29" t="s">
-        <v>17</v>
-      </c>
-      <c r="G29" t="s">
-        <v>17</v>
-      </c>
-      <c r="H29">
-        <v>60</v>
+        <v>25</v>
+      </c>
+      <c r="G29">
+        <v>60</v>
+      </c>
+      <c r="H29" t="s">
+        <v>68</v>
       </c>
       <c r="I29" t="s">
-        <v>26</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="A30" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" t="s">
         <v>14</v>
       </c>
-      <c r="B30" t="s">
-        <v>27</v>
-      </c>
-      <c r="C30" t="s">
-        <v>16</v>
-      </c>
       <c r="D30" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F30" t="s">
-        <v>17</v>
-      </c>
-      <c r="G30" t="s">
-        <v>17</v>
-      </c>
-      <c r="H30">
-        <v>60</v>
+        <v>16</v>
+      </c>
+      <c r="G30">
+        <v>60</v>
+      </c>
+      <c r="H30" t="s">
+        <v>70</v>
       </c>
       <c r="I30" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>14</v>
+      <c r="A31" s="2">
+        <v>46141</v>
       </c>
       <c r="B31" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" t="s">
         <v>20</v>
       </c>
-      <c r="D31" t="s">
-        <v>1</v>
-      </c>
       <c r="E31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F31" t="s">
-        <v>17</v>
-      </c>
-      <c r="G31" t="s">
-        <v>17</v>
-      </c>
-      <c r="H31">
-        <v>60</v>
+        <v>16</v>
+      </c>
+      <c r="G31">
+        <v>60</v>
+      </c>
+      <c r="H31" t="s">
+        <v>72</v>
       </c>
       <c r="I31" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>14</v>
+      <c r="A32" s="2">
+        <v>46141</v>
       </c>
       <c r="B32" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
         <v>23</v>
       </c>
       <c r="D32" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E32" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F32" t="s">
-        <v>17</v>
-      </c>
-      <c r="G32" t="s">
-        <v>17</v>
-      </c>
-      <c r="H32">
-        <v>60</v>
+        <v>25</v>
+      </c>
+      <c r="G32">
+        <v>60</v>
+      </c>
+      <c r="H32" t="s">
+        <v>74</v>
       </c>
       <c r="I32" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="A33" s="2">
+        <v>46141</v>
+      </c>
+      <c r="B33" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" t="s">
         <v>14</v>
       </c>
-      <c r="B33" t="s">
-        <v>22</v>
-      </c>
-      <c r="C33" t="s">
-        <v>16</v>
-      </c>
       <c r="D33" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F33" t="s">
-        <v>17</v>
-      </c>
-      <c r="G33" t="s">
-        <v>17</v>
-      </c>
-      <c r="H33">
-        <v>60</v>
+        <v>16</v>
+      </c>
+      <c r="G33">
+        <v>60</v>
+      </c>
+      <c r="H33" t="s">
+        <v>76</v>
       </c>
       <c r="I33" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>14</v>
+      <c r="A34" s="2">
+        <v>46141</v>
       </c>
       <c r="B34" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C34" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" t="s">
         <v>20</v>
       </c>
-      <c r="D34" t="s">
-        <v>1</v>
-      </c>
       <c r="E34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F34" t="s">
-        <v>17</v>
-      </c>
-      <c r="G34" t="s">
-        <v>17</v>
-      </c>
-      <c r="H34">
-        <v>60</v>
+        <v>16</v>
+      </c>
+      <c r="G34">
+        <v>60</v>
+      </c>
+      <c r="H34" t="s">
+        <v>78</v>
       </c>
       <c r="I34" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>14</v>
+      <c r="A35" s="2">
+        <v>46141</v>
       </c>
       <c r="B35" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C35" t="s">
         <v>23</v>
       </c>
       <c r="D35" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E35" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F35" t="s">
-        <v>17</v>
-      </c>
-      <c r="G35" t="s">
-        <v>17</v>
-      </c>
-      <c r="H35">
-        <v>60</v>
+        <v>25</v>
+      </c>
+      <c r="G35">
+        <v>60</v>
+      </c>
+      <c r="H35" t="s">
+        <v>80</v>
       </c>
       <c r="I35" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
